--- a/tools/importer/reports/import-careers-content-page.report.xlsx
+++ b/tools/importer/reports/import-careers-content-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>careers.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","columns","columns"]</t>
+  </si>
+  <si>
+    <t>careers</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>careers-content-page</t>
+  </si>
+  <si>
+    <t>2026-04-02T00:24:02.720Z</t>
+  </si>
+  <si>
+    <t>Careers | Alberta Blue Cross®</t>
+  </si>
+  <si>
+    <t>https://www.careers.ab.bluecross.ca/</t>
+  </si>
+  <si>
     <t>careers/benefits.report.json</t>
   </si>
   <si>
@@ -46,12 +70,6 @@
     <t>careers/benefits</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>careers-content-page</t>
-  </si>
-  <si>
     <t>2026-04-01T22:56:37.728Z</t>
   </si>
   <si>
@@ -116,9 +134,6 @@
   </si>
   <si>
     <t>careers/values.report.json</t>
-  </si>
-  <si>
-    <t>["hero","columns","columns","columns"]</t>
   </si>
   <si>
     <t>careers/values</t>
@@ -519,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -687,6 +702,32 @@
         <v>39</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
